--- a/data/trans_camb/IP19C08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Edad-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,95</t>
+          <t>0,0; 52,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,73</t>
+          <t>0,0; 28,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 4,47</t>
+          <t>-10,37; 3,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 4,46</t>
+          <t>-9,31; 4,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 0,44</t>
+          <t>-11,6; 0,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 3,94</t>
+          <t>-8,03; 4,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; -0,86</t>
+          <t>-11,64; -1,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 0,73</t>
+          <t>-11,26; 0,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 2,23</t>
+          <t>-6,64; 1,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -0,1</t>
+          <t>-8,47; -0,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -1,21</t>
+          <t>-8,81; -0,86</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-80,08; 103,01</t>
+          <t>-82,15; 90,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,74; 103,22</t>
+          <t>-77,74; 137,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,36; 32,01</t>
+          <t>-91,31; 72,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 124,38</t>
+          <t>-76,08; 124,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,88</t>
+          <t>-100,0; 40,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,81; 48,73</t>
+          <t>-66,53; 39,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,99; 4,76</t>
+          <t>-82,46; 0,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-85,92; -12,85</t>
+          <t>-86,66; -14,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 3,43</t>
+          <t>-7,63; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 0,42</t>
+          <t>-9,69; 0,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 0,08</t>
+          <t>-10,66; 0,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 1,65</t>
+          <t>-7,85; 1,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,56</t>
+          <t>-7,78; 1,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,37</t>
+          <t>-8,13; 1,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 1,32</t>
+          <t>-6,42; 1,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -0,08</t>
+          <t>-7,21; -0,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -0,64</t>
+          <t>-7,54; -0,62</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 90,1</t>
+          <t>-66,78; 87,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,59; 26,36</t>
+          <t>-84,04; 23,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,66; 13,94</t>
+          <t>-89,14; 11,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,77; 62,06</t>
+          <t>-80,31; 63,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,78; 51,5</t>
+          <t>-78,36; 60,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-80,47; 52,7</t>
+          <t>-81,37; 39,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 28,08</t>
+          <t>-66,76; 22,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,2; 0,84</t>
+          <t>-72,27; 0,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-80,41; -9,88</t>
+          <t>-78,68; -6,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,51</t>
+          <t>-3,95; 1,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,46</t>
+          <t>-2,97; 3,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; -0,16</t>
+          <t>-5,3; -0,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 3,07</t>
+          <t>-2,85; 3,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,6</t>
+          <t>-3,97; 1,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 6,67</t>
+          <t>-2,31; 7,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,27</t>
+          <t>-2,81; 1,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,5</t>
+          <t>-2,72; 1,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,13</t>
+          <t>-2,72; 2,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-87,54; 134,64</t>
+          <t>-85,91; 150,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 219,81</t>
+          <t>-69,76; 249,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,04</t>
+          <t>-100,0; 29,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 217,39</t>
+          <t>-71,22; 210,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 142,57</t>
+          <t>-100,0; 135,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 430,29</t>
+          <t>-71,08; 788,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 68,62</t>
+          <t>-69,19; 81,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,53; 71,14</t>
+          <t>-71,86; 85,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 167,42</t>
+          <t>-73,27; 163,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,29</t>
+          <t>-4,28; 1,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,75</t>
+          <t>-4,53; 0,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -1,4</t>
+          <t>-6,07; -1,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,32</t>
+          <t>-3,75; 1,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,21</t>
+          <t>-4,47; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,58</t>
+          <t>-4,01; 1,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,52</t>
+          <t>-3,16; 0,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,23</t>
+          <t>-3,82; -0,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,34</t>
+          <t>-4,17; -0,36</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 31,32</t>
+          <t>-59,58; 26,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 19,33</t>
+          <t>-62,9; 22,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,87; -28,99</t>
+          <t>-81,98; -27,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 41,08</t>
+          <t>-58,44; 38,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 10,55</t>
+          <t>-72,14; 9,23</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 49,33</t>
+          <t>-65,86; 62,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 13,32</t>
+          <t>-50,89; 11,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-59,72; -4,41</t>
+          <t>-60,35; -5,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,0; -5,12</t>
+          <t>-67,38; -7,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Edad-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,54</t>
+          <t>0,0; 58,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,28</t>
+          <t>0,0; 33,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 3,66</t>
+          <t>-9,4; 3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 4,63</t>
+          <t>-9,56; 3,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 0,99</t>
+          <t>-11,89; 0,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 4,2</t>
+          <t>-7,86; 3,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -1,19</t>
+          <t>-10,99; -0,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 0,12</t>
+          <t>-10,84; 0,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,97</t>
+          <t>-6,66; 2,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -0,58</t>
+          <t>-8,97; -0,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -0,86</t>
+          <t>-9,35; -0,86</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,15; 90,15</t>
+          <t>-80,32; 97,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,74; 137,68</t>
+          <t>-80,65; 88,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-91,31; 72,64</t>
+          <t>-92,79; 37,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,08; 124,88</t>
+          <t>-78,78; 109,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 75,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,54</t>
+          <t>-93,33; 42,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,53; 39,88</t>
+          <t>-65,43; 70,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,46; 0,82</t>
+          <t>-84,81; 7,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-86,66; -14,94</t>
+          <t>-88,08; -13,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 3,77</t>
+          <t>-7,78; 3,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 0,51</t>
+          <t>-9,96; 0,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 0,02</t>
+          <t>-10,55; -0,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 1,64</t>
+          <t>-7,61; 1,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 1,86</t>
+          <t>-7,04; 2,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 1,06</t>
+          <t>-7,99; 1,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,14</t>
+          <t>-6,64; 1,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,2</t>
+          <t>-7,06; -0,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; -0,62</t>
+          <t>-7,64; -0,42</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 87,88</t>
+          <t>-68,87; 89,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-84,04; 23,39</t>
+          <t>-82,94; 20,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,14; 11,73</t>
+          <t>-89,13; 21,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,31; 63,96</t>
+          <t>-82,62; 61,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,36; 60,32</t>
+          <t>-75,74; 80,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 39,54</t>
+          <t>-79,99; 46,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 22,82</t>
+          <t>-64,54; 27,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,27; 0,63</t>
+          <t>-73,4; 0,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,68; -6,2</t>
+          <t>-77,45; 1,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,85</t>
+          <t>-4,32; 1,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,59</t>
+          <t>-3,42; 3,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -0,24</t>
+          <t>-4,93; 0,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 3,06</t>
+          <t>-2,85; 3,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,49</t>
+          <t>-3,79; 1,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 7,61</t>
+          <t>-2,29; 6,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,48</t>
+          <t>-2,73; 1,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,72</t>
+          <t>-2,74; 1,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,79</t>
+          <t>-2,54; 2,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-85,91; 150,98</t>
+          <t>-87,63; 117,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,76; 249,38</t>
+          <t>-75,28; 190,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,31</t>
+          <t>-94,55; 52,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 210,01</t>
+          <t>-73,35; 195,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 135,52</t>
+          <t>-100,0; 164,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 788,78</t>
+          <t>-68,82; 516,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,19; 81,17</t>
+          <t>-66,83; 93,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-71,86; 85,11</t>
+          <t>-69,39; 78,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,27; 163,99</t>
+          <t>-71,28; 142,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,06</t>
+          <t>-4,36; 0,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,87</t>
+          <t>-4,54; 0,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -1,31</t>
+          <t>-5,87; -1,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,27</t>
+          <t>-3,61; 1,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,12</t>
+          <t>-4,63; 0,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,87</t>
+          <t>-3,99; 1,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,43</t>
+          <t>-3,17; 0,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,34</t>
+          <t>-3,81; -0,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,36</t>
+          <t>-4,23; -0,51</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 26,06</t>
+          <t>-60,84; 24,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-62,9; 22,04</t>
+          <t>-62,76; 18,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,98; -27,66</t>
+          <t>-81,15; -26,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 38,3</t>
+          <t>-58,58; 46,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 9,23</t>
+          <t>-73,75; 2,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 62,66</t>
+          <t>-66,02; 53,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 11,28</t>
+          <t>-50,27; 13,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,35; -5,23</t>
+          <t>-60,15; -3,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-67,38; -7,5</t>
+          <t>-68,31; -6,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,72</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>13,3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,16</t>
+          <t>7,51</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 51,62</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,63</t>
+          <t>0,0; 28,54</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-5,39</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,72</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,67</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,39</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-5,08</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,83</t>
+          <t>-4,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 3,99</t>
+          <t>-8,16; 3,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 3,67</t>
+          <t>-11,27; -0,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 0,67</t>
+          <t>-10,39; 0,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 3,59</t>
+          <t>-9,76; 4,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -0,68</t>
+          <t>-9,02; 4,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 0,47</t>
+          <t>-11,6; 0,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 2,94</t>
+          <t>-6,89; 2,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; -0,14</t>
+          <t>-8,68; -0,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,35; -0,86</t>
+          <t>-9,31; -1,28</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-24,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-78,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-68,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-32,35%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-31,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-60,51%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-24,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-78,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-65,02%</t>
+          <t>-60,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-63,08%</t>
+          <t>-64,4%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-80,32; 97,08</t>
+          <t>-77,91; 124,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,65; 88,24</t>
+          <t>-100,0; 50,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-92,79; 37,32</t>
+          <t>-100,0; 50,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-78,78; 109,83</t>
+          <t>-80,08; 103,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,55</t>
+          <t>-78,74; 103,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-93,33; 42,82</t>
+          <t>-90,53; 43,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 70,01</t>
+          <t>-66,81; 48,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,81; 7,08</t>
+          <t>-81,99; 4,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-88,08; -13,13</t>
+          <t>-86,55; -13,85</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,81</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,43</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,18</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,76</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,81</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,43</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-3,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 3,71</t>
+          <t>-7,73; 1,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 0,5</t>
+          <t>-8,11; 1,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,55; -0,01</t>
+          <t>-8,14; 1,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 1,73</t>
+          <t>-7,94; 3,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,39</t>
+          <t>-10,0; 0,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 1,36</t>
+          <t>-10,24; 0,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,08</t>
+          <t>-5,93; 1,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -0,14</t>
+          <t>-7,27; -0,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; -0,42</t>
+          <t>-7,81; -0,64</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-43,03%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-37,16%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-44,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-20,72%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-53,44%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-60,8%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-43,03%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-37,16%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-44,92%</t>
+          <t>-60,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-52,88%</t>
+          <t>-52,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 89,39</t>
+          <t>-80,77; 62,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,94; 20,99</t>
+          <t>-80,78; 51,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,13; 21,02</t>
+          <t>-80,3; 56,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,62; 61,97</t>
+          <t>-68,77; 90,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 80,25</t>
+          <t>-82,59; 26,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,99; 46,48</t>
+          <t>-90,02; 15,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 27,06</t>
+          <t>-64,31; 28,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,4; 0,76</t>
+          <t>-72,2; 0,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,45; 1,32</t>
+          <t>-80,48; -8,88</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,07</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,37</t>
+          <t>-2,96; 3,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,22</t>
+          <t>-3,83; 1,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,05</t>
+          <t>-2,55; 6,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 3,14</t>
+          <t>-4,32; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,84</t>
+          <t>-3,05; 3,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,38</t>
+          <t>-5,19; -0,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,6</t>
+          <t>-2,77; 1,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,62</t>
+          <t>-2,63; 1,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,8</t>
+          <t>-2,58; 3,19</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-0,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-39,93%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-41,67%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-2,09%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-69,16%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-0,05%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-39,93%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>-69,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,16%</t>
+          <t>-21,62%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 117,66</t>
+          <t>-74,1; 217,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,28; 190,41</t>
+          <t>-100,0; 142,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-94,55; 52,92</t>
+          <t>-77,3; 453,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-73,35; 195,64</t>
+          <t>-87,54; 134,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 164,99</t>
+          <t>-71,29; 219,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 516,83</t>
+          <t>-100,0; 26,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,83; 93,05</t>
+          <t>-66,97; 68,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,39; 78,85</t>
+          <t>-67,53; 71,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 142,69</t>
+          <t>-69,57; 173,1</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,89</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,95</t>
+          <t>-3,66; 1,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,79</t>
+          <t>-4,45; 0,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -1,18</t>
+          <t>-4,01; 1,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,4</t>
+          <t>-4,22; 1,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,02</t>
+          <t>-4,65; 0,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,69</t>
+          <t>-6,29; -1,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,57</t>
+          <t>-2,95; 0,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,23</t>
+          <t>-3,69; -0,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,51</t>
+          <t>-3,99; -0,33</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-22,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-45,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-30,27%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-26,21%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-33,18%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-61,23%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-22,0%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-45,24%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-30,05%</t>
+          <t>-61,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-45,7%</t>
+          <t>-46,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 24,26</t>
+          <t>-58,29; 41,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-62,76; 18,43</t>
+          <t>-72,3; 10,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,15; -26,09</t>
+          <t>-65,87; 53,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 46,11</t>
+          <t>-58,01; 31,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 2,91</t>
+          <t>-63,25; 19,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 53,05</t>
+          <t>-82,04; -29,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 13,74</t>
+          <t>-48,09; 13,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,15; -3,77</t>
+          <t>-59,72; -4,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -6,83</t>
+          <t>-65,62; -5,19</t>
         </is>
       </c>
     </row>
